--- a/site/Entra-ID-Namely-Integration-Setup-Guide/headings.xlsx
+++ b/site/Entra-ID-Namely-Integration-Setup-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Integration Scenarios</t>
+          <t>Integration Features</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Worker Sync Settings</t>
+          <t>User Management</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,73 +705,73 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Candidate Management</t>
+          <t>Source Filter</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
+          <t>h_01KPZ3WYP3Y687Y87QFYRDDJ1A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPZ3WYP3Y687Y87QFYRDDJ1A</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Writeback Settings</t>
+          <t>Safeguard Limits</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
+          <t>h_01KPZ3XJ5V5RYQZ75X6V7KM7KM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPZ3XJ5V5RYQZ75X6V7KM7KM</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Candidate Management</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KPTV18DWG3VBTF717Q0AMST6</t>
+          <t>h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DWG3VBTF717Q0AMST6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Worker to SFTP</t>
+          <t>Writeback Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,41 +781,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Candidate to SFTP</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+          <t>h_01KPTV18DWG3VBTF717Q0AMST6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DWG3VBTF717Q0AMST6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Writeback Map</t>
+          <t>Worker to SFTP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Candidate to SFTP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Writeback Map</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,63 +891,63 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,98 +979,142 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Failure Execution</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Entra-ID-Namely-Integration-Setup-Guide/headings.xlsx
+++ b/site/Entra-ID-Namely-Integration-Setup-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -749,95 +749,95 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Candidate Management</t>
+          <t>Creation Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
+          <t>h_01KPZ4EN4MQV44NEYMCCG7925K</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPZ4EN4MQV44NEYMCCG7925K</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Writeback Settings</t>
+          <t>Update Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
+          <t>h_01KPZ4FHP9M99377Z9CMFFRS1N</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPZ4FHP9M99377Z9CMFFRS1N</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Deactivation Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KPTV18DWG3VBTF717Q0AMST6</t>
+          <t>h_01KPZ4FR5N9VH5G5G9CE6QCW59</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DWG3VBTF717Q0AMST6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPZ4FR5N9VH5G5G9CE6QCW59</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Worker to SFTP</t>
+          <t>User Correlation Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Candidate to SFTP</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,63 +847,63 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+          <t>h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Writeback Map</t>
+          <t>Unique UPN Generation</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+          <t>h_01KPZAT7P4QD0Y2C0XYMK519FC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPZAT7P4QD0Y2C0XYMK519FC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01KPTV18DWG3VBTF717Q0AMST6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DWG3VBTF717Q0AMST6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Worker to SFTP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Candidate to SFTP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,186 +935,274 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Writeback Map</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Failure Execution</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Notification Report Settings</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Entra-ID-Namely-Integration-Setup-Guide/headings.xlsx
+++ b/site/Entra-ID-Namely-Integration-Setup-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,51 +881,51 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Unique Email Generation</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KPTV18DWG3VBTF717Q0AMST6</t>
+          <t>h_01KPZVFWA74PB7VJ6887QRYPP9</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DWG3VBTF717Q0AMST6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPZVFWA74PB7VJ6887QRYPP9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Worker to SFTP</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>h_01KPTV18DWG3VBTF717Q0AMST6</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DWG3VBTF717Q0AMST6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Candidate to SFTP</t>
+          <t>Worker to SFTP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Writeback Map</t>
+          <t>Candidate to SFTP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+          <t>h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Writeback Map</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,41 +1023,41 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Failure Execution</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,98 +1111,120 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Entra-ID-Namely-Integration-Setup-Guide/headings.xlsx
+++ b/site/Entra-ID-Namely-Integration-Setup-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,51 +903,51 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Unique Password Generation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KPTV18DWG3VBTF717Q0AMST6</t>
+          <t>h_01KQ6K5M545G3V76AP4E2JK0BR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DWG3VBTF717Q0AMST6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KQ6K5M545G3V76AP4E2JK0BR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Worker to SFTP</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>h_01KPTV18DWG3VBTF717Q0AMST6</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DWG3VBTF717Q0AMST6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Candidate to SFTP</t>
+          <t>Worker to SFTP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Writeback Map</t>
+          <t>Candidate to SFTP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+          <t>h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Writeback Map</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,41 +1045,41 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,19 +1111,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Failure Execution</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,98 +1133,120 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Entra-ID-Namely-Integration-Setup-Guide/headings.xlsx
+++ b/site/Entra-ID-Namely-Integration-Setup-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,129 +913,129 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KQ6K5M545G3V76AP4E2JK0BR</t>
+          <t>h_01KQ6XED8HMR8ZH48Z10QFSRC7</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KQ6K5M545G3V76AP4E2JK0BR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KQ6XED8HMR8ZH48Z10QFSRC7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>User Date Offset</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KPTV18DWG3VBTF717Q0AMST6</t>
+          <t>h_01KQ6NS444PZJ29BH3PQB26C0T</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DWG3VBTF717Q0AMST6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KQ6NS444PZJ29BH3PQB26C0T</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Worker to SFTP</t>
+          <t>Onboarding User Date Offset</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>h_01KQ6P2MF13MP4ZC1G2GYHXB7J</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KQ6P2MF13MP4ZC1G2GYHXB7J</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Candidate to SFTP</t>
+          <t>Offboarding User Date Offset</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+          <t>h_01KQ6XED8H2NXYV0PW3F14WHZ7</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KQ6XED8H2NXYV0PW3F14WHZ7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Writeback Map</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+          <t>h_01KPTV18DWG3VBTF717Q0AMST6</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPTV18DWG3VBTF717Q0AMST6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Group Rules</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Group Assignment Rules</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,19 +1045,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KQ6X33G7W7RDPKAX1CRPAREG</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KQ6X33G7W7RDPKAX1CRPAREG</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,19 +1133,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,98 +1155,142 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Failure Execution</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Entra-ID-Namely-Integration-Setup-Guide/headings.xlsx
+++ b/site/Entra-ID-Namely-Integration-Setup-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>h_01KQ70EAMGYJ63NA72H8NF3DHJ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KQ70EAMGYJ63NA72H8NF3DHJ</t>
         </is>
       </c>
     </row>
@@ -1045,107 +1045,107 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KQ6X33G7W7RDPKAX1CRPAREG</t>
+          <t>h_01KQ70EG7WE97W5S09BV62VABM</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KQ6X33G7W7RDPKAX1CRPAREG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KQ70EG7WE97W5S09BV62VABM</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Using Condition Builder</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01KM0H9RTRKRPWDXNTDVVVD7FR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KM0H9RTRKRPWDXNTDVVVD7FR</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Using Expressions</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KM0HAHDDAJMYYBC477MCE3Z9</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KM0HAHDDAJMYYBC477MCE3Z9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>License Rules</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>License Assignment Rules</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01KQ6X33G7W7RDPKAX1CRPAREG</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KQ6X33G7W7RDPKAX1CRPAREG</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>Using Condition Builder</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,19 +1155,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01KQ70FA33YSJEP1Z9GR50TH3X</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KQ70FA33YSJEP1Z9GR50TH3X</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>Using Expressions</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1177,41 +1177,41 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>h_01KQ70FEMDKQ3X9E5437GYC6NT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KQ70FEMDKQ3X9E5437GYC6NT</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1221,76 +1221,252 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Success Execution</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Failure Execution</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Create Notification</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Update Notification</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>h_01KQ71VR7Z6WZCHQCH96SZ5RE9</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KQ71VR7Z6WZCHQCH96SZ5RE9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Deactivate Notification</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>h_01KQ71VR7ZQNYG5V6ZNPRNMWMB</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01KQ71VR7ZQNYG5V6ZNPRNMWMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Namely-Integration-Setup-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
